--- a/target/classes/input.xlsx
+++ b/target/classes/input.xlsx
@@ -3,19 +3,15 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RadheyshyamRavi\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B98407F2-850C-4AE3-AD76-900E452C2119}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{DAD7D209-58BF-4BE5-B87B-27CEAD094871}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1860" yWindow="1860" windowWidth="14400" windowHeight="7270" xr2:uid="{747226A8-A7BE-41B5-B583-EA9B8645BB99}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{747226A8-A7BE-41B5-B583-EA9B8645BB99}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="0"/>
+  <oleSize ref="A1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="16">
   <si>
     <t>employee_id</t>
   </si>
@@ -93,7 +89,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -109,12 +105,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF0D0D0D"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="8"/>
       <color rgb="FF0D0D0D"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -140,16 +130,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -485,10 +472,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34526BAF-CFBA-422E-922F-B5B07A7F109C}">
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:8" ht="42" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" customFormat="1" ht="42" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -514,7 +501,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -540,489 +527,513 @@
         <v>72</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2">
+        <v>28</v>
+      </c>
+      <c r="C3" s="2">
+        <v>45000</v>
+      </c>
+      <c r="D3" s="2">
+        <v>3</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="2">
         <v>2</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B4" s="2">
         <v>35</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C4" s="2">
         <v>72000</v>
       </c>
-      <c r="D3" s="2">
-        <v>10</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="D4" s="2">
+        <v>10</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="2">
+      <c r="H4" s="2">
         <v>88</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A4" s="2">
+    <row r="5" spans="1:8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="2">
         <v>3</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B5" s="2">
         <v>42</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C5" s="2">
         <v>95000</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D5" s="2">
         <v>18</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G4" s="2" t="s">
+      <c r="F5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="H4" s="2">
+      <c r="H5" s="2">
         <v>91</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A5" s="2">
+    <row r="6" spans="1:8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="2">
         <v>4</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B6" s="2">
         <v>29</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C6" s="2">
         <v>48000</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D6" s="2">
         <v>4</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H5" s="2">
+      <c r="G6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H6" s="2">
         <v>65</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A6" s="2">
+    <row r="7" spans="1:8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="2">
         <v>5</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2">
+      <c r="B7" s="2"/>
+      <c r="C7" s="2">
         <v>61000</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D7" s="2">
         <v>7</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H6" s="2">
+      <c r="F7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H7" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A7" s="2">
+    <row r="8" spans="1:8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="2">
         <v>6</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B8" s="2">
         <v>38</v>
       </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2">
+      <c r="C8" s="2"/>
+      <c r="D8" s="2">
         <v>12</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F8" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="G8" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H7" s="2">
+      <c r="H8" s="2">
         <v>85</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A8" s="2">
+    <row r="9" spans="1:8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="2">
         <v>7</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B9" s="2">
         <v>25</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C9" s="2">
         <v>39000</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D9" s="2">
         <v>1</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E9" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2">
+      <c r="F9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2">
         <v>60</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A9" s="2">
+    <row r="10" spans="1:8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="2">
         <v>8</v>
       </c>
-      <c r="B9" s="2">
+      <c r="B10" s="2">
         <v>33</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C10" s="2">
         <v>67000</v>
       </c>
-      <c r="D9" s="2">
-        <v>9</v>
-      </c>
-      <c r="E9" s="2" t="s">
+      <c r="D10" s="2">
+        <v>9</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2" t="s">
+      <c r="F10" s="2"/>
+      <c r="G10" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H9" s="2">
+      <c r="H10" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A10" s="2">
-        <v>9</v>
-      </c>
-      <c r="B10" s="2">
+    <row r="11" spans="1:8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="2">
+        <v>9</v>
+      </c>
+      <c r="B11" s="2">
         <v>45</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C11" s="2">
         <v>105000</v>
       </c>
-      <c r="D10" s="2">
+      <c r="D11" s="2">
         <v>20</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E11" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G10" s="2" t="s">
+      <c r="F11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G11" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="H10" s="2">
+      <c r="H11" s="2">
         <v>95</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A11" s="2">
-        <v>10</v>
-      </c>
-      <c r="B11" s="2">
+    <row r="12" spans="1:8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="2">
+        <v>10</v>
+      </c>
+      <c r="B12" s="2">
         <v>31</v>
       </c>
-      <c r="C11" s="2">
+      <c r="C12" s="2">
         <v>54000</v>
       </c>
-      <c r="D11" s="2">
+      <c r="D12" s="2">
         <v>6</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E12" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="F12" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G11" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H11" s="2">
+      <c r="G12" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H12" s="2">
         <v>70</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A12" s="2">
+    <row r="13" spans="1:8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="2">
         <v>11</v>
       </c>
-      <c r="B12" s="2">
+      <c r="B13" s="2">
         <v>27</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C13" s="2">
         <v>42000</v>
       </c>
-      <c r="D12" s="2">
+      <c r="D13" s="2">
         <v>2</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E13" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F12" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H12" s="2">
+      <c r="F13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H13" s="2">
         <v>68</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A13" s="2">
+    <row r="14" spans="1:8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="2">
         <v>12</v>
       </c>
-      <c r="B13" s="2">
+      <c r="B14" s="2">
         <v>36</v>
       </c>
-      <c r="C13" s="2">
+      <c r="C14" s="2">
         <v>78000</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D14" s="2">
         <v>11</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="E14" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="F14" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G13" s="2" t="s">
+      <c r="G14" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H13" s="2">
+      <c r="H14" s="2">
         <v>87</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A14" s="2">
+    <row r="15" spans="1:8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="2">
         <v>13</v>
       </c>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2">
+      <c r="B15" s="2"/>
+      <c r="C15" s="2">
         <v>55000</v>
       </c>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2" t="s">
+      <c r="D15" s="2"/>
+      <c r="E15" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F14" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H14" s="2">
+      <c r="F15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H15" s="2">
         <v>74</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A15" s="2">
+    <row r="16" spans="1:8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="2">
         <v>14</v>
       </c>
-      <c r="B15" s="2">
+      <c r="B16" s="2">
         <v>40</v>
       </c>
-      <c r="C15" s="2">
+      <c r="C16" s="2">
         <v>88000</v>
       </c>
-      <c r="D15" s="2">
+      <c r="D16" s="2">
         <v>15</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="E16" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="F16" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G15" s="2" t="s">
+      <c r="G16" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="H15" s="2">
+      <c r="H16" s="2">
         <v>90</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A16" s="2">
+    <row r="17" spans="1:8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="2">
         <v>15</v>
       </c>
-      <c r="B16" s="2">
+      <c r="B17" s="2">
         <v>30</v>
       </c>
-      <c r="C16" s="2">
+      <c r="C17" s="2">
         <v>51000</v>
       </c>
-      <c r="D16" s="2">
+      <c r="D17" s="2">
         <v>5</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="E17" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F16" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H16" s="2">
+      <c r="F17" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H17" s="2">
         <v>69</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A17" s="2">
+    <row r="18" spans="1:8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="2">
         <v>16</v>
       </c>
-      <c r="B17" s="2">
+      <c r="B18" s="2">
         <v>35</v>
       </c>
-      <c r="C17" s="2">
+      <c r="C18" s="2">
         <v>72000</v>
       </c>
-      <c r="D17" s="2">
-        <v>10</v>
-      </c>
-      <c r="E17" s="2" t="s">
+      <c r="D18" s="2">
+        <v>10</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F17" s="2" t="s">
+      <c r="F18" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G17" s="2" t="s">
+      <c r="G18" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H17" s="2">
+      <c r="H18" s="2">
         <v>88</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A18" s="2">
+    <row r="19" spans="1:8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="2">
         <v>17</v>
       </c>
-      <c r="B18" s="2">
+      <c r="B19" s="2">
         <v>28</v>
       </c>
-      <c r="C18" s="2">
+      <c r="C19" s="2">
         <v>45000</v>
       </c>
-      <c r="D18" s="2">
+      <c r="D19" s="2">
         <v>3</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="E19" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F18" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H18" s="2">
+      <c r="F19" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H19" s="2">
         <v>72</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A19" s="2">
+    <row r="20" spans="1:8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="2">
         <v>18</v>
       </c>
-      <c r="B19" s="2">
+      <c r="B20" s="2">
         <v>52</v>
       </c>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2">
+      <c r="C20" s="2"/>
+      <c r="D20" s="2">
         <v>25</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="E20" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F19" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G19" s="2" t="s">
+      <c r="F20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G20" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="H19" s="2">
+      <c r="H20" s="2">
         <v>93</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A20" s="2">
+    <row r="21" spans="1:8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="2">
         <v>19</v>
       </c>
-      <c r="B20" s="2">
+      <c r="B21" s="2">
         <v>24</v>
       </c>
-      <c r="C20" s="2">
+      <c r="C21" s="2">
         <v>37000</v>
       </c>
-      <c r="D20" s="2">
+      <c r="D21" s="2">
         <v>1</v>
       </c>
-      <c r="E20" s="2" t="s">
+      <c r="E21" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F20" s="2" t="s">
+      <c r="F21" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G20" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H20" s="2">
+      <c r="G21" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H21" s="2">
         <v>58</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A21" s="2">
+    <row r="22" spans="1:8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="2">
         <v>20</v>
       </c>
-      <c r="B21" s="2">
+      <c r="B22" s="2">
         <v>39</v>
       </c>
-      <c r="C21" s="2">
+      <c r="C22" s="2">
         <v>83000</v>
       </c>
-      <c r="D21" s="2">
+      <c r="D22" s="2">
         <v>14</v>
       </c>
-      <c r="E21" s="2" t="s">
+      <c r="E22" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F21" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G21" s="2" t="s">
+      <c r="F22" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G22" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H21" s="2">
+      <c r="H22" s="2">
         <v>86</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A22" s="3"/>
-    </row>
+    <row r="23" spans="1:8" customFormat="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
